--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104720_W30.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104720_W30.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.528</v>
+        <v>7.3042</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1883</v>
+        <v>5.6622</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3396</v>
+        <v>1.642</v>
       </c>
       <c r="G2" t="n">
-        <v>9.295500000000001</v>
+        <v>9.293100000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2893</v>
+        <v>2.2939</v>
       </c>
       <c r="I2" t="n">
-        <v>7.0062</v>
+        <v>6.9992</v>
       </c>
       <c r="J2" t="n">
-        <v>6.6649</v>
+        <v>6.6498</v>
       </c>
       <c r="K2" t="n">
-        <v>1.538</v>
+        <v>1.5341</v>
       </c>
       <c r="L2" t="n">
-        <v>5.1268</v>
+        <v>5.1157</v>
       </c>
       <c r="M2" t="n">
-        <v>2.6307</v>
+        <v>2.6434</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7513</v>
+        <v>0.7598</v>
       </c>
       <c r="O2" t="n">
-        <v>1.8794</v>
+        <v>1.8835</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.4759</v>
+        <v>-1.701</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1134</v>
+        <v>0.3782</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.3625</v>
+        <v>-2.0793</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.2004</v>
+        <v>-1.1984</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2004</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5237</v>
+        <v>6.9783</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0683</v>
+        <v>4.5355</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4554</v>
+        <v>2.4428</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9766</v>
+        <v>1.9742</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3216</v>
+        <v>0.3191</v>
       </c>
       <c r="I3" t="n">
-        <v>1.655</v>
+        <v>1.6551</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4053</v>
+        <v>0.393</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1564</v>
+        <v>0.1477</v>
       </c>
       <c r="L3" t="n">
-        <v>0.249</v>
+        <v>0.2453</v>
       </c>
       <c r="M3" t="n">
-        <v>1.5713</v>
+        <v>1.5812</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1652</v>
+        <v>0.1715</v>
       </c>
       <c r="O3" t="n">
-        <v>1.406</v>
+        <v>1.4097</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1632</v>
+        <v>-0.7000999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.044</v>
+        <v>0.448</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.1192</v>
+        <v>-1.148</v>
       </c>
       <c r="V3" t="n">
-        <v>4.8015</v>
+        <v>4.7937</v>
       </c>
       <c r="W3" t="n">
-        <v>5.07</v>
+        <v>5.0604</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2685</v>
+        <v>-0.2667</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2985</v>
+        <v>4.0622</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8065</v>
+        <v>3.4318</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4919</v>
+        <v>0.6304</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5295</v>
+        <v>3.5229</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8686</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6609</v>
+        <v>2.6554</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1661</v>
+        <v>3.1498</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3946</v>
+        <v>1.3855</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7715</v>
+        <v>1.7644</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3634</v>
+        <v>0.373</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.526</v>
+        <v>-0.518</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8894</v>
+        <v>0.8911</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2988</v>
+        <v>-1.5305</v>
       </c>
       <c r="T4" t="n">
-        <v>0.322</v>
+        <v>-0.0351</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.6208</v>
+        <v>-1.4954</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9318</v>
+        <v>0.9317</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5456</v>
+        <v>0.5447</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3862</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="5">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
+        <v>3.1416</v>
+      </c>
+      <c r="E5" t="n">
         <v>2.9061</v>
       </c>
-      <c r="E5" t="n">
-        <v>2.6808</v>
-      </c>
       <c r="F5" t="n">
-        <v>0.2253</v>
+        <v>0.2355</v>
       </c>
       <c r="G5" t="n">
-        <v>1.676</v>
+        <v>1.6758</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6853</v>
+        <v>-1.6832</v>
       </c>
       <c r="I5" t="n">
-        <v>3.3613</v>
+        <v>3.359</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2142</v>
+        <v>2.207</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.731</v>
+        <v>-0.7347</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9452</v>
+        <v>2.9417</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5382</v>
+        <v>-0.5312</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9543</v>
+        <v>-0.9485</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4161</v>
+        <v>0.4173</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9971</v>
+        <v>-0.7619</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3975</v>
+        <v>-0.1628</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5996</v>
+        <v>-0.5991</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0283</v>
+        <v>1.1984</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2413</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.787</v>
+        <v>0.2522</v>
       </c>
       <c r="G6" t="n">
-        <v>3.4753</v>
+        <v>3.4822</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4095</v>
+        <v>1.4125</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0658</v>
+        <v>2.0697</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1602</v>
+        <v>1.1547</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9738</v>
+        <v>0.9685</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1864</v>
+        <v>0.1862</v>
       </c>
       <c r="M6" t="n">
-        <v>2.3151</v>
+        <v>2.3275</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4357</v>
+        <v>0.444</v>
       </c>
       <c r="O6" t="n">
-        <v>1.8794</v>
+        <v>1.8835</v>
       </c>
       <c r="P6" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4951</v>
+        <v>-1.3421</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6945</v>
+        <v>0.406</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.1895</v>
+        <v>-1.7482</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.9967</v>
+        <v>-2.9904</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3862</v>
+        <v>-0.387</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.6104</v>
+        <v>-2.6034</v>
       </c>
     </row>
     <row r="7">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2028</v>
+        <v>0.3535</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1346</v>
+        <v>-0.0238</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3374</v>
+        <v>0.3773</v>
       </c>
       <c r="G7" t="n">
-        <v>0.263</v>
+        <v>0.2687</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5545</v>
+        <v>-0.5492</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8175</v>
+        <v>0.8179</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2555</v>
+        <v>0.2551</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0689</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1864</v>
+        <v>0.1862</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0075</v>
+        <v>0.0135</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6237</v>
+        <v>-0.6182</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6311</v>
+        <v>0.6317</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8565</v>
+        <v>-0.7071</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2776</v>
+        <v>-0.1604</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5788</v>
+        <v>-0.5468</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W. FALK</t>
+          <t>H. SANT-ROOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4025</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5042</v>
+        <v>-0.9355</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1017</v>
+        <v>0.418</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.495</v>
+        <v>1.5018</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4884</v>
+        <v>2.1169</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0066</v>
+        <v>-0.6151</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3908</v>
+        <v>0.5956</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7137</v>
+        <v>2.7784</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6771</v>
+        <v>-2.1827</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1042</v>
+        <v>0.9062</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2254</v>
+        <v>-0.6615</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3295</v>
+        <v>1.5677</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1359</v>
+        <v>-1.5934</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3631</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8653</v>
+        <v>-1.7511</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0225</v>
+        <v>-0.0955</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1573</v>
+        <v>-1.6556</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.4959</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.6536999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. SANT-ROOS</t>
+          <t>T. NAKIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5284</v>
+        <v>-1.1201</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8669</v>
+        <v>-1.4013</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3385</v>
+        <v>0.2812</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5031</v>
+        <v>-0.6036</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1196</v>
+        <v>-0.7449</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6165</v>
+        <v>0.1413</v>
       </c>
       <c r="J9" t="n">
-        <v>0.608</v>
+        <v>-0.9622000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>2.7883</v>
+        <v>0.1034</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.1803</v>
+        <v>-1.0656</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8951</v>
+        <v>0.3586</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6688</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>1.5638</v>
+        <v>1.2069</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2272</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.5903</v>
+        <v>-1.3658</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8175</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.7633</v>
+        <v>-1.606</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.044</v>
+        <v>-0.1628</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.7194</v>
+        <v>-1.4432</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.4953</v>
+        <v>1.0895</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1594</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6548</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. NAKIC</t>
+          <t>W. FALK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.516</v>
+        <v>-1.1835</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6275</v>
+        <v>-2.2016</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1115</v>
+        <v>1.0181</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6098</v>
+        <v>-1.4936</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7529</v>
+        <v>-0.4882</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1431</v>
+        <v>-1.0054</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9582000000000001</v>
+        <v>-1.3954</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1037</v>
+        <v>-0.7174</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.0619</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3484</v>
+        <v>-0.0982</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8566</v>
+        <v>0.2292</v>
       </c>
       <c r="O10" t="n">
-        <v>1.205</v>
+        <v>-0.3275</v>
       </c>
       <c r="P10" t="n">
+        <v>0.2276</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-1.1382</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.3658</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.0825</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.2494</v>
+      </c>
+      <c r="V10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-1.3631</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.3631</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-1.9975</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-0.3975</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.0913</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.0913</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0083</v>
+        <v>-2.0671</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.6155</v>
+        <v>-4.5608</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6071</v>
+        <v>2.4936</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5302</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7912</v>
+        <v>0.7924</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.261</v>
+        <v>-0.2607</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3735</v>
+        <v>-1.3781</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0924</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.466</v>
+        <v>-1.4676</v>
       </c>
       <c r="M11" t="n">
-        <v>1.9037</v>
+        <v>1.9099</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6987</v>
+        <v>0.703</v>
       </c>
       <c r="O11" t="n">
-        <v>1.205</v>
+        <v>1.2069</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0447</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.635</v>
+        <v>-3.6421</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5441</v>
+        <v>-0.5991</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2336</v>
+        <v>0.3017</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7778</v>
+        <v>-0.9008</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0503</v>
+        <v>0.0488</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1091</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9858</v>
+        <v>-2.3955</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3362</v>
+        <v>-2.9191</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3505</v>
+        <v>0.5236</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.522</v>
+        <v>-1.519</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.825</v>
+        <v>-0.8218</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.697</v>
+        <v>-0.6972</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.5917</v>
+        <v>-2.5959</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.1631</v>
+        <v>-1.1656</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4287</v>
+        <v>-1.4303</v>
       </c>
       <c r="M12" t="n">
-        <v>1.0697</v>
+        <v>1.077</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3381</v>
+        <v>0.3438</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7317</v>
+        <v>0.7331</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.508</v>
+        <v>0.0732</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3914</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8995</v>
+        <v>-0.7418</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.4101</v>
+        <v>-1.405</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4101</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>15.0464</v>
+        <v>15.7544</v>
       </c>
       <c r="E13" t="n">
-        <v>4.9003</v>
+        <v>5.439600000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>10.1459</v>
+        <v>10.3147</v>
       </c>
       <c r="G13" t="n">
-        <v>18.6224</v>
+        <v>18.6343</v>
       </c>
       <c r="H13" t="n">
-        <v>3.4937</v>
+        <v>3.514899999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>15.1287</v>
+        <v>15.1192</v>
       </c>
       <c r="J13" t="n">
-        <v>8.16</v>
+        <v>8.073399999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5085</v>
+        <v>4.4582</v>
       </c>
       <c r="L13" t="n">
-        <v>3.651299999999999</v>
+        <v>3.615399999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>10.4625</v>
+        <v>10.5609</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.015</v>
+        <v>-0.9431999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>11.4774</v>
+        <v>11.5039</v>
       </c>
       <c r="P13" t="n">
-        <v>4.5436</v>
+        <v>4.5526</v>
       </c>
       <c r="Q13" t="n">
-        <v>-13.6311</v>
+        <v>-13.6579</v>
       </c>
       <c r="R13" t="n">
-        <v>18.1749</v>
+        <v>18.2105</v>
       </c>
       <c r="S13" t="n">
-        <v>-11.2342</v>
+        <v>-10.5432</v>
       </c>
       <c r="T13" t="n">
-        <v>1.39</v>
+        <v>2.0642</v>
       </c>
       <c r="U13" t="n">
-        <v>-12.6244</v>
+        <v>-12.6076</v>
       </c>
       <c r="V13" t="n">
-        <v>3.1144</v>
+        <v>3.1107</v>
       </c>
       <c r="W13" t="n">
-        <v>8.9815</v>
+        <v>8.959899999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.8671</v>
+        <v>-5.849100000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. KARNIK</t>
+          <t>M. GEBEN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.01</v>
+        <v>2.3061</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4716</v>
+        <v>1.9681</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4616</v>
+        <v>0.3381</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6233</v>
+        <v>1.206</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6118</v>
+        <v>1.5681</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.9885</v>
+        <v>-0.3621</v>
       </c>
       <c r="J14" t="n">
-        <v>2.492</v>
+        <v>0.8594000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>4.0326</v>
+        <v>1.9995</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.5405</v>
+        <v>-1.1401</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.8688</v>
+        <v>0.3467</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4208</v>
+        <v>-0.4314</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.448</v>
+        <v>0.778</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.7262</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.635</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9087</v>
+        <v>1.1382</v>
       </c>
       <c r="S14" t="n">
-        <v>3.107</v>
+        <v>1.4156</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4995</v>
+        <v>1.7021</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6076</v>
+        <v>-0.2865</v>
       </c>
       <c r="V14" t="n">
-        <v>2.006</v>
+        <v>-0.3155</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1151</v>
+        <v>0.5447</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1091</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. GEBEN</t>
+          <t>S. MARTINEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6259</v>
+        <v>1.6466</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3355</v>
+        <v>0.5706</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2904</v>
+        <v>1.0759</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2073</v>
+        <v>0.8546</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5688</v>
+        <v>0.5888</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3615</v>
+        <v>0.2657</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8682</v>
+        <v>0.8222</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0046</v>
+        <v>0.7477</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.1364</v>
+        <v>0.0745</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3391</v>
+        <v>0.0324</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4358</v>
+        <v>-0.1588</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7749</v>
+        <v>0.1912</v>
       </c>
       <c r="P15" t="n">
+        <v>-0.6829</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-2.2763</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.5934</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.6327</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.0248</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.3921</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.1578</v>
+      </c>
+      <c r="W15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-1.1359</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.1359</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.7374</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.0576</v>
-      </c>
-      <c r="U15" t="n">
-        <v>-0.3202</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-0.3188</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.5456</v>
-      </c>
       <c r="X15" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. MARTINEZ</t>
+          <t>J. KARNIK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6452</v>
+        <v>1.4074</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0573</v>
+        <v>2.1385</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5879</v>
+        <v>-0.731</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8515</v>
+        <v>0.6159</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5898</v>
+        <v>3.6025</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2616</v>
+        <v>-2.9866</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8297</v>
+        <v>2.4774</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7552</v>
+        <v>4.0194</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0746</v>
+        <v>-1.542</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0217</v>
+        <v>-1.8615</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1654</v>
+        <v>-0.4169</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1871</v>
+        <v>-1.4446</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6816</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2719</v>
+        <v>-3.6421</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5903</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6347</v>
+        <v>1.5246</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4995</v>
+        <v>1.1957</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8648</v>
+        <v>0.3289</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1594</v>
+        <v>1.9986</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.1075</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1594</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5476</v>
+        <v>0.2623</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0216</v>
+        <v>0.6637</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.474</v>
+        <v>-0.4014</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9799</v>
+        <v>-0.9785</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7649</v>
+        <v>-0.764</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.215</v>
+        <v>-0.2144</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7198</v>
+        <v>-0.7207</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7198</v>
+        <v>-0.7207</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2601</v>
+        <v>-0.2578</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0451</v>
+        <v>-0.0433</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.215</v>
+        <v>-0.2144</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6191</v>
+        <v>0.3287</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6501</v>
+        <v>0.2949</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.031</v>
+        <v>0.0338</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2268</v>
+        <v>0.2292</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. NEEDHAM</t>
+          <t>O. LIVINGSTON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1058</v>
+        <v>-0.753</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6768</v>
+        <v>-1.3363</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7826</v>
+        <v>0.5833</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2466</v>
+        <v>0.1032</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3652</v>
+        <v>0.5012</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6117</v>
+        <v>-0.398</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3104</v>
+        <v>0.4577</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0571</v>
+        <v>0.6745</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3674</v>
+        <v>-0.2169</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0638</v>
+        <v>-0.3544</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3081</v>
+        <v>-0.1733</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2443</v>
+        <v>-0.1811</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9087</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2719</v>
+        <v>-3.4145</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3631</v>
+        <v>1.5934</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7388</v>
+        <v>0.8071</v>
       </c>
       <c r="T18" t="n">
-        <v>2.6383</v>
+        <v>1.4628</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8995</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.1825</v>
+        <v>0.1578</v>
       </c>
       <c r="W18" t="n">
+        <v>0.1578</v>
+      </c>
+      <c r="X18" t="n">
         <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-2.1825</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4677</v>
+        <v>-1.0175</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0696</v>
+        <v>-0.7181999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.398</v>
+        <v>-0.2994</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3012</v>
+        <v>-1.2999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5057</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.8068</v>
+        <v>-1.8053</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.426</v>
+        <v>-0.4277</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3629</v>
+        <v>0.362</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7889</v>
+        <v>-0.7896</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8752</v>
+        <v>-0.8722</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1427</v>
+        <v>0.1435</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0179</v>
+        <v>-1.0157</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2846</v>
+        <v>0.1637</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4164</v>
+        <v>-0.0629</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1319</v>
+        <v>0.2265</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1091</v>
+        <v>-0.1089</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1091</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. LIVINGSTON</t>
+          <t>D. NEEDHAM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9336</v>
+        <v>-1.3297</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2482</v>
+        <v>0.1219</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3146</v>
+        <v>-1.4516</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1164</v>
+        <v>1.2454</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5125</v>
+        <v>-0.3648</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3961</v>
+        <v>1.6102</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4825</v>
+        <v>1.3</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6929</v>
+        <v>-0.0624</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2104</v>
+        <v>1.3624</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3661</v>
+        <v>-0.0546</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1804</v>
+        <v>-0.3023</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1857</v>
+        <v>0.2477</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.8175</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4078</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5903</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3919</v>
+        <v>0.5144</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5177</v>
+        <v>1.0982</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9096</v>
+        <v>-0.5838</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1594</v>
+        <v>-2.1789</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1594</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="21">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6475</v>
+        <v>-1.8814</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2437</v>
+        <v>-2.4202</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5962</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.218</v>
+        <v>-3.2191</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3246</v>
+        <v>-1.324</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.8934</v>
+        <v>-1.8951</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.8273</v>
+        <v>-2.8311</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4606</v>
+        <v>-0.4621</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.3667</v>
+        <v>-2.3689</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3907</v>
+        <v>-0.3881</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8641</v>
+        <v>-0.8618</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4733</v>
+        <v>0.4738</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1111</v>
+        <v>0.6549</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4164</v>
+        <v>0.4109</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3054</v>
+        <v>0.244</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3595</v>
+        <v>-3.1479</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6995</v>
+        <v>-0.4709</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.66</v>
+        <v>-2.677</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.0127</v>
+        <v>-3.0107</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5921</v>
+        <v>-0.5916</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.4206</v>
+        <v>-2.4191</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.359</v>
+        <v>-1.3637</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1443</v>
+        <v>0.1411</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.5032</v>
+        <v>-1.5048</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6537</v>
+        <v>-1.6471</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7363</v>
+        <v>-0.7328</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9174</v>
+        <v>-0.9143</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4905</v>
+        <v>0.6954</v>
       </c>
       <c r="T22" t="n">
-        <v>0.341</v>
+        <v>0.5757</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1495</v>
+        <v>0.1198</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.746</v>
+        <v>-1.7432</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5456</v>
+        <v>0.5447</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.2916</v>
+        <v>-2.2879</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. HUGHES</t>
+          <t>C. HILDRETH</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0901</v>
+        <v>-3.739</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8816</v>
+        <v>-2.3965</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2085</v>
+        <v>-1.3425</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.5891</v>
+        <v>-4.3426</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.9122</v>
+        <v>-3.1497</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.6769</v>
+        <v>-1.1929</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.4752</v>
+        <v>-3.0114</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.1458</v>
+        <v>-2.259</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.3294</v>
+        <v>-0.7524</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.1139</v>
+        <v>-1.3312</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7664</v>
+        <v>-0.8907</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.3474</v>
+        <v>-0.4405</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1359</v>
+        <v>-1.3658</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5903</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>2.1358</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>1.7295</v>
+        <v>0.5757</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4063</v>
+        <v>0.2766</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0913</v>
+        <v>0.2066</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.405</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0913</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="24">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2916</v>
+        <v>-3.9947</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.0047</v>
+        <v>-5.6631</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7131</v>
+        <v>1.6684</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.226</v>
+        <v>-4.2237</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.1782</v>
+        <v>-2.177</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.0478</v>
+        <v>-2.0467</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.6355</v>
+        <v>-4.6429</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.3434</v>
+        <v>-2.3484</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.2921</v>
+        <v>-2.2945</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4096</v>
+        <v>0.4192</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1652</v>
+        <v>0.1715</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2443</v>
+        <v>0.2477</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>0.9522</v>
+        <v>1.2484</v>
       </c>
       <c r="T24" t="n">
-        <v>1.1299</v>
+        <v>1.4837</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1776</v>
+        <v>-0.2353</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1091</v>
+        <v>-0.1089</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1091</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C. HILDRETH</t>
+          <t>M. HUGHES</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.9792</v>
+        <v>-4.0269</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.5613</v>
+        <v>-2.7723</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4179</v>
+        <v>-1.2546</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.3407</v>
+        <v>-5.5849</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.1451</v>
+        <v>-1.91</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.1957</v>
+        <v>-3.6748</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.0026</v>
+        <v>-3.4801</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.2509</v>
+        <v>-1.1484</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.7516</v>
+        <v>-2.3317</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.3382</v>
+        <v>-2.1048</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.8941</v>
+        <v>-0.7617</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.444</v>
+        <v>-1.3432</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.3631</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9087</v>
+        <v>1.5934</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3938</v>
+        <v>2.1922</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6057</v>
+        <v>1.8459</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2119</v>
+        <v>0.3463</v>
       </c>
       <c r="V25" t="n">
-        <v>0.2097</v>
+        <v>-1.0895</v>
       </c>
       <c r="W25" t="n">
-        <v>1.4101</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2004</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-15.0463</v>
+        <v>-14.2677</v>
       </c>
       <c r="E26" t="n">
-        <v>-10.1458</v>
+        <v>-10.3147</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.900400000000001</v>
+        <v>-3.953</v>
       </c>
       <c r="G26" t="n">
-        <v>-18.6225</v>
+        <v>-18.6343</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.4937</v>
+        <v>-3.515000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-15.129</v>
+        <v>-15.1191</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.4626</v>
+        <v>-10.5609</v>
       </c>
       <c r="K26" t="n">
-        <v>1.014900000000001</v>
+        <v>0.9431999999999996</v>
       </c>
       <c r="L26" t="n">
-        <v>-11.4772</v>
+        <v>-11.504</v>
       </c>
       <c r="M26" t="n">
-        <v>-8.1601</v>
+        <v>-8.073399999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>-4.5086</v>
+        <v>-4.458</v>
       </c>
       <c r="O26" t="n">
-        <v>-3.6515</v>
+        <v>-3.6154</v>
       </c>
       <c r="P26" t="n">
-        <v>-4.543599999999999</v>
+        <v>-4.5527</v>
       </c>
       <c r="Q26" t="n">
-        <v>-18.175</v>
+        <v>-18.2105</v>
       </c>
       <c r="R26" t="n">
-        <v>13.6311</v>
+        <v>13.6579</v>
       </c>
       <c r="S26" t="n">
-        <v>11.2341</v>
+        <v>12.03</v>
       </c>
       <c r="T26" t="n">
-        <v>12.6246</v>
+        <v>12.6075</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.3901</v>
+        <v>-0.5774999999999997</v>
       </c>
       <c r="V26" t="n">
-        <v>-3.1143</v>
+        <v>-3.110500000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>5.8671</v>
+        <v>5.8492</v>
       </c>
       <c r="X26" t="n">
-        <v>-8.981299999999999</v>
+        <v>-8.9598</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104720_W30.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104720_W30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104720_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.2667</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104720_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104720_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104720_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.6034</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104720_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104720_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.6536999999999999</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104720_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104720_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104720_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104720_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104720_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-5.849100000000001</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104720_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104720_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104720_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104720_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104720_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104720_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104720_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104720_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.2879</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104720_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104720_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104720_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104720_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-8.9598</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
